--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-29).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-29).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-170</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 893.880,47</t>
-  </si>
-  <si>
-    <t>R$ 4.938,57
-R$ 5.072,73</t>
-  </si>
-  <si>
-    <t>(14.0%)
-(11.7%)</t>
-  </si>
-  <si>
-    <t>52.0</t>
-  </si>
-  <si>
-    <t>(14.7%)</t>
-  </si>
-  <si>
-    <t>36.3%</t>
-  </si>
-  <si>
-    <t>(17.3%)</t>
+175</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 910.281,93</t>
+  </si>
+  <si>
+    <t>R$ 4.893,99
+R$ 5.021,52</t>
+  </si>
+  <si>
+    <t>(13.8%)
+(11.5%)</t>
+  </si>
+  <si>
+    <t>51.5</t>
+  </si>
+  <si>
+    <t>(14.5%)</t>
+  </si>
+  <si>
+    <t>26.2%</t>
+  </si>
+  <si>
+    <t>(27.1%)</t>
   </si>
   <si>
     <t>3.6%</t>
@@ -947,13 +947,13 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>26.4</t>
-  </si>
-  <si>
-    <t>76.3%</t>
-  </si>
-  <si>
-    <t>8.4%</t>
+    <t>26.5</t>
+  </si>
+  <si>
+    <t>76.2%</t>
+  </si>
+  <si>
+    <t>8.5%</t>
   </si>
   <si>
     <t>5.5</t>
@@ -965,13 +965,13 @@
     <t>11.8</t>
   </si>
   <si>
-    <t>18.3</t>
-  </si>
-  <si>
-    <t>74.4%</t>
-  </si>
-  <si>
-    <t>-R$ 29.763,48</t>
+    <t>18.4</t>
+  </si>
+  <si>
+    <t>74.3%</t>
+  </si>
+  <si>
+    <t>-R$ 29.866,68</t>
   </si>
   <si>
     <t>2.94</t>
@@ -3025,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>8.5071428571428562</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>17.465616000000001</v>
+      </c>
       <c r="AD13" s="8">
         <v>23.383050847457625</v>
       </c>
@@ -5841,10 +5843,10 @@
         <v>0.30769230769230771</v>
       </c>
       <c r="T35" s="6">
-        <v>30.40593247356761</v>
+        <v>3.1570995214851374</v>
       </c>
       <c r="U35" s="6">
-        <v>27.939008237420225</v>
+        <v>0.69017528533775219</v>
       </c>
       <c r="V35" s="6">
         <v>0.12004854194059691</v>
@@ -5922,7 +5924,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5958,25 +5960,59 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="O36" s="5">
+        <v>4367.1099999999997</v>
+      </c>
+      <c r="P36" s="5">
+        <v>4367.1099999999997</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-0.18318339100346026</v>
+      </c>
+      <c r="R36" s="7">
+        <v>43</v>
+      </c>
+      <c r="S36" s="6">
+        <v>-0.022727272727272707</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.35171264291487964</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.014861590388151432</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.079900895557931909</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.035711488833576437</v>
+      </c>
+      <c r="X36" s="8">
+        <v>32.401332000000004</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>6.7746204545454551</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>12.218054166666667</v>
+      </c>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="AD36" s="8">
+        <v>25.765331999999997</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.76000000000000001</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6668,7 +6704,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6704,25 +6740,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>4331.0799999999999</v>
+      </c>
+      <c r="P42" s="5">
+        <v>4331.0799999999999</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.095316854569089005</v>
+      </c>
+      <c r="R42" s="7">
+        <v>51</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.04081632653061229</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.36895628803901104</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.054702106633911174</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.062883276226714815</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.013138178006409488</v>
+      </c>
+      <c r="X42" s="8">
+        <v>27.370312500000001</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.2634744680851071</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>7.1338531249999999</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>14.321353999999999</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>21.276562500000001</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.6875</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -7803,7 +7875,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7839,25 +7911,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>980.60000000000002</v>
+      </c>
+      <c r="P51" s="5">
+        <v>980.60000000000002</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.033891625615763532</v>
+      </c>
+      <c r="R51" s="7">
+        <v>9</v>
+      </c>
+      <c r="S51" s="6">
+        <v>0</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.38977156842749333</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.044290230471140113</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.086252294513563116</v>
+      </c>
+      <c r="X51" s="8">
+        <v>21.523339999999997</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>3.9799999999999995</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>8.8133400000000002</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>18.953340000000001</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8730,7 +8836,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>13.281333</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -10984,7 +11092,9 @@
       <c r="AB76" s="8">
         <v>4.1080645161290317</v>
       </c>
-      <c r="AC76" s="8"/>
+      <c r="AC76" s="8">
+        <v>7.4840439999999999</v>
+      </c>
       <c r="AD76" s="8">
         <v>16.033333333333335</v>
       </c>
@@ -14180,7 +14290,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14216,25 +14326,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>2280.3099999999999</v>
+      </c>
+      <c r="P102" s="5">
+        <v>2280.3099999999999</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.18763448521553261</v>
+      </c>
+      <c r="R102" s="7">
+        <v>23</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.2068965517241379</v>
+      </c>
+      <c r="T102" s="6">
+        <v>7.0429020615618045E-05</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.37025641250531727</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.027957382987400838</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.0057266336594585824</v>
+      </c>
+      <c r="X102" s="8">
+        <v>35.034261111111114</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>6.6388875000000001</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>8.9813705882352934</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>15.739705000000001</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>21.79815</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.44444444444444442</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>-81.400000000000006</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -17056,7 +17202,7 @@
         <v>0.053072060889164732</v>
       </c>
       <c r="W125" s="6">
-        <v>0.019078332734459216</v>
+        <v>0.020690392970306733</v>
       </c>
       <c r="X125" s="8">
         <v>30.934847727272725</v>
@@ -21449,7 +21595,7 @@
         <v>0.045730943993971283</v>
       </c>
       <c r="W160" s="6">
-        <v>0.0085671152668671275</v>
+        <v>0.0077540325679283494</v>
       </c>
       <c r="X160" s="8">
         <v>29.423214285714288</v>
@@ -24776,7 +24922,9 @@
       <c r="AB186" s="8">
         <v>4.5750000000000002</v>
       </c>
-      <c r="AC186" s="8"/>
+      <c r="AC186" s="8">
+        <v>9.46875</v>
+      </c>
       <c r="AD186" s="8">
         <v>16.422912499999999</v>
       </c>
@@ -25875,7 +26023,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25911,25 +26059,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>4442.3599999999997</v>
+      </c>
+      <c r="P195" s="5">
+        <v>4442.3599999999997</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>0.15075121749041531</v>
+      </c>
+      <c r="R195" s="7">
+        <v>51</v>
+      </c>
+      <c r="S195" s="6">
+        <v>-0.019230769230769273</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.34577647916873017</v>
+      </c>
+      <c r="U195" s="6">
+        <v>-0.0080422117973329502</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.015449896001224575</v>
+      </c>
+      <c r="W195" s="6">
+        <v>-0.010844686157808012</v>
+      </c>
+      <c r="X195" s="8">
+        <v>28.757290625</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0.03125</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>6.3996369565217393</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>8.0656250000000007</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>22.025521874999999</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.625</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-21.800000000000001</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>
@@ -27401,7 +27583,9 @@
       <c r="AB207" s="8">
         <v>7.8037000000000001</v>
       </c>
-      <c r="AC207" s="8"/>
+      <c r="AC207" s="8">
+        <v>16.012962000000002</v>
+      </c>
       <c r="AD207" s="8">
         <v>22.955555555555556</v>
       </c>
